--- a/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>NECB</t>
   </si>
@@ -656,123 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42004</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41639</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41274</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>40908</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40543</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40178</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>39813</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E8" s="3">
         <v>72000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>48400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>49000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53800</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
         <v>19900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,9 +824,12 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,9 +998,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1030,9 +1049,12 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E17" s="3">
         <v>8600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15800</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E18" s="3">
         <v>63400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38100</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>16700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,74 +1244,78 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-29000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-24100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-22600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-21100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-14200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9600</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E21" s="3">
         <v>35700</v>
-      </c>
-      <c r="E21" s="3">
-        <v>16700</v>
       </c>
       <c r="F21" s="3">
         <v>16700</v>
       </c>
       <c r="G21" s="3">
+        <v>16700</v>
+      </c>
+      <c r="H21" s="3">
         <v>17800</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1292,24 +1328,27 @@
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E23" s="3">
         <v>34400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>15600</v>
       </c>
       <c r="F23" s="3">
         <v>15600</v>
       </c>
       <c r="G23" s="3">
+        <v>15600</v>
+      </c>
+      <c r="H23" s="3">
         <v>16900</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>2500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E24" s="3">
         <v>9600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E26" s="3">
         <v>24800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13000</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E27" s="3">
         <v>24800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13000</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E32" s="3">
         <v>29000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>24100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>22600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>21100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>14200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9600</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E33" s="3">
         <v>24800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13000</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E35" s="3">
         <v>24800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13000</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42004</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41639</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41274</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>40908</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40543</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40178</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>39813</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,104 +2158,111 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E41" s="3">
         <v>13200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43200</v>
-      </c>
-      <c r="K41" s="3">
-        <v>3700</v>
       </c>
       <c r="L41" s="3">
         <v>3700</v>
       </c>
       <c r="M41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N41" s="3">
         <v>2800</v>
-      </c>
-      <c r="N41" s="3">
-        <v>2500</v>
       </c>
       <c r="O41" s="3">
         <v>2500</v>
       </c>
       <c r="P41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q41" s="3">
         <v>3400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E42" s="3">
         <v>83400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>63300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>112000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="3">
-        <v>32400</v>
+      <c r="K42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L42" s="3">
         <v>32400</v>
       </c>
       <c r="M42" s="3">
+        <v>32400</v>
+      </c>
+      <c r="N42" s="3">
         <v>48200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>84300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>46800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>96300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>37000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2216,9 +2308,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2264,9 +2359,12 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2312,9 +2410,12 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2360,41 +2461,44 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E47" s="3">
         <v>18000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2408,65 +2512,71 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E48" s="3">
         <v>30200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
-        <v>11700</v>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>11700</v>
       </c>
       <c r="M48" s="3">
+        <v>11700</v>
+      </c>
+      <c r="N48" s="3">
         <v>12900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>700</v>
       </c>
       <c r="F49" s="3">
         <v>700</v>
@@ -2474,8 +2584,8 @@
       <c r="G49" s="3">
         <v>700</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
+      <c r="H49" s="3">
+        <v>700</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>5</v>
@@ -2483,30 +2593,33 @@
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K49" s="3">
-        <v>1000</v>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L49" s="3">
         <v>1000</v>
       </c>
       <c r="M49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N49" s="3">
         <v>1500</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1800</v>
       </c>
       <c r="O49" s="3">
         <v>1800</v>
       </c>
       <c r="P49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,41 +2716,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>3900</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>3700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
+      <c r="M52" s="3">
+        <v>3700</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
@@ -2648,9 +2767,12 @@
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1764100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1425000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1225100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>968200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>955200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>870300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>814800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>734500</v>
-      </c>
-      <c r="K54" s="3">
-        <v>515400</v>
       </c>
       <c r="L54" s="3">
         <v>515400</v>
       </c>
       <c r="M54" s="3">
+        <v>515400</v>
+      </c>
+      <c r="N54" s="3">
         <v>444200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>489300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>466000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>527300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>424200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,56 +2914,60 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E57" s="3">
         <v>14800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8500</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
-        <v>4200</v>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L57" s="3">
         <v>4200</v>
       </c>
       <c r="M57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2880,27 +3013,30 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2913,8 +3049,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -2928,9 +3064,12 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2976,14 +3115,17 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
         <v>500</v>
@@ -2992,11 +3134,11 @@
         <v>500</v>
       </c>
       <c r="G61" s="3">
+        <v>500</v>
+      </c>
+      <c r="H61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -3024,9 +3166,12 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3072,9 +3217,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1484800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1163000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>973700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>814400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>813100</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K66" s="3">
-        <v>411600</v>
+      <c r="K66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L66" s="3">
         <v>411600</v>
       </c>
       <c r="M66" s="3">
+        <v>411600</v>
+      </c>
+      <c r="N66" s="3">
         <v>340400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>382200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>357900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>419800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>313700</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E72" s="3">
         <v>132700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>114300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>105300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>93800</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
-        <v>55500</v>
+      <c r="K72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L72" s="3">
         <v>55500</v>
       </c>
       <c r="M72" s="3">
+        <v>55500</v>
+      </c>
+      <c r="N72" s="3">
         <v>53900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>54100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>57400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,35 +3850,38 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>279300</v>
+      </c>
+      <c r="E76" s="3">
         <v>262000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>251400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>153800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>142100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>129600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>116900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>109500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>103800</v>
       </c>
       <c r="L76" s="3">
         <v>103800</v>
@@ -3705,20 +3890,23 @@
         <v>103800</v>
       </c>
       <c r="N76" s="3">
+        <v>103800</v>
+      </c>
+      <c r="O76" s="3">
         <v>107100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>108100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>107400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>110500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42004</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41639</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41274</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>40908</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40543</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40178</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>39813</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E81" s="3">
         <v>24800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13000</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,8 +4083,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3895,17 +4093,17 @@
         <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F83" s="3">
         <v>1100</v>
       </c>
       <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3918,24 +4116,27 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>700</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
       </c>
       <c r="O83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>800</v>
       </c>
       <c r="Q83" s="3">
+        <v>800</v>
+      </c>
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E89" s="3">
         <v>27500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>1700</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>1700</v>
       </c>
       <c r="M89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N89" s="3">
         <v>600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>-100</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,27 +4611,30 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-357800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-256600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-178900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4418,24 +4647,27 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>7000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>13100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-84200</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,26 +4686,27 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-6900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-800</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -4481,19 +4714,19 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>-500</v>
       </c>
       <c r="M96" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N96" s="3">
         <v>-700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-600</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-700</v>
       </c>
       <c r="P96" s="3">
         <v>-700</v>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>-700</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,27 +4887,30 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E100" s="3">
         <v>172100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>240400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>69400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4678,24 +4923,27 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-41000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-64000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>108800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>78400</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4720,14 +4968,14 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4741,55 +4989,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-57000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>83100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-58500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>76300</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>-17700</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>-17700</v>
       </c>
       <c r="M102" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="N102" s="3">
         <v>-33300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>38100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-44300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>52200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>NECB</t>
   </si>
@@ -732,25 +732,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>132500</v>
+        <v>99800</v>
       </c>
       <c r="E8" s="3">
-        <v>72000</v>
+        <v>65100</v>
       </c>
       <c r="F8" s="3">
-        <v>48400</v>
+        <v>42000</v>
       </c>
       <c r="G8" s="3">
-        <v>49000</v>
+        <v>40700</v>
       </c>
       <c r="H8" s="3">
-        <v>53800</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
+        <v>40900</v>
+      </c>
+      <c r="I8" s="3">
+        <v>39600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>33000</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>5</v>
@@ -833,26 +833,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>65100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>42000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>40700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>39600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>33000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1007,26 +1007,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1128,25 +1128,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>36300</v>
+        <v>35000</v>
       </c>
       <c r="E17" s="3">
-        <v>8600</v>
+        <v>29600</v>
       </c>
       <c r="F17" s="3">
-        <v>8700</v>
+        <v>26400</v>
       </c>
       <c r="G17" s="3">
-        <v>10800</v>
+        <v>24700</v>
       </c>
       <c r="H17" s="3">
-        <v>15800</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
+        <v>23800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>18400</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1179,25 +1179,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>96200</v>
+        <v>64800</v>
       </c>
       <c r="E18" s="3">
-        <v>63400</v>
+        <v>35500</v>
       </c>
       <c r="F18" s="3">
-        <v>39700</v>
+        <v>15700</v>
       </c>
       <c r="G18" s="3">
-        <v>38200</v>
+        <v>16000</v>
       </c>
       <c r="H18" s="3">
-        <v>38100</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
+        <v>17100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>14600</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1251,25 +1251,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-31500</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>-29000</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
-        <v>-24100</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>-22600</v>
+        <v>300</v>
       </c>
       <c r="H20" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1305,22 +1305,22 @@
         <v>66000</v>
       </c>
       <c r="E21" s="3">
-        <v>35700</v>
+        <v>36100</v>
       </c>
       <c r="F21" s="3">
         <v>16700</v>
       </c>
       <c r="G21" s="3">
-        <v>16700</v>
+        <v>16800</v>
       </c>
       <c r="H21" s="3">
         <v>17800</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="I21" s="3">
+        <v>17600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>15300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1352,26 +1352,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1418,11 +1418,11 @@
       <c r="H23" s="3">
         <v>16900</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
+      <c r="I23" s="3">
+        <v>16800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>14500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -1571,11 +1571,11 @@
       <c r="H26" s="3">
         <v>13000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
+      <c r="I26" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8100</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -1620,13 +1620,13 @@
         <v>12300</v>
       </c>
       <c r="H27" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I27" s="3">
         <v>13000</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
+      <c r="J27" s="3">
+        <v>8100</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -1863,25 +1863,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>31500</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>29000</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
-        <v>24100</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>22600</v>
+        <v>-300</v>
       </c>
       <c r="H32" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -1928,11 +1928,11 @@
       <c r="H33" s="3">
         <v>13000</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
+      <c r="I33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>8100</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -2030,11 +2030,11 @@
       <c r="H35" s="3">
         <v>13000</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
+      <c r="I35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>8100</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -2165,19 +2165,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13400</v>
+        <v>68700</v>
       </c>
       <c r="E41" s="3">
-        <v>13200</v>
+        <v>95300</v>
       </c>
       <c r="F41" s="3">
-        <v>8300</v>
+        <v>152300</v>
       </c>
       <c r="G41" s="3">
-        <v>7600</v>
+        <v>69200</v>
       </c>
       <c r="H41" s="3">
-        <v>17200</v>
+        <v>127700</v>
       </c>
       <c r="I41" s="3">
         <v>51400</v>
@@ -2216,25 +2216,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>56300</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>83400</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>145600</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>63300</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>112000</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>100</v>
+      </c>
+      <c r="J42" s="3">
+        <v>200</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>5</v>
@@ -2266,26 +2266,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2318,25 +2318,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2369,25 +2369,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>12300</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2420,25 +2420,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>82500</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>105500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>158600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>75100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>133900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>57700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>49400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2471,25 +2471,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18100</v>
+        <v>34800</v>
       </c>
       <c r="E47" s="3">
-        <v>18000</v>
+        <v>45600</v>
       </c>
       <c r="F47" s="3">
-        <v>19900</v>
+        <v>39300</v>
       </c>
       <c r="G47" s="3">
-        <v>10300</v>
+        <v>19200</v>
       </c>
       <c r="H47" s="3">
-        <v>10000</v>
+        <v>20500</v>
       </c>
       <c r="I47" s="3">
-        <v>8800</v>
+        <v>14800</v>
       </c>
       <c r="J47" s="3">
-        <v>6900</v>
+        <v>14000</v>
       </c>
       <c r="K47" s="3">
         <v>3900</v>
@@ -2522,25 +2522,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31800</v>
+        <v>30400</v>
       </c>
       <c r="E48" s="3">
-        <v>30200</v>
+        <v>28700</v>
       </c>
       <c r="F48" s="3">
-        <v>28300</v>
+        <v>26800</v>
       </c>
       <c r="G48" s="3">
-        <v>23600</v>
+        <v>22100</v>
       </c>
       <c r="H48" s="3">
-        <v>21700</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
+        <v>20100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>13100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
@@ -2587,11 +2587,11 @@
       <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+      <c r="I49" s="3">
+        <v>800</v>
+      </c>
+      <c r="J49" s="3">
+        <v>900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -2726,25 +2726,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3900</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+        <v>30700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>29400</v>
+      </c>
+      <c r="G52" s="3">
+        <v>29000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>29800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>30900</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2921,25 +2921,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>13600</v>
+        <v>1407700</v>
       </c>
       <c r="E57" s="3">
-        <v>14800</v>
+        <v>1130900</v>
       </c>
       <c r="F57" s="3">
-        <v>13500</v>
+        <v>934800</v>
       </c>
       <c r="G57" s="3">
-        <v>8900</v>
+        <v>775200</v>
       </c>
       <c r="H57" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
+        <v>782800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>690400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>627600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
@@ -2972,25 +2972,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>57700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>40400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3022,20 +3022,20 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1200</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -3074,25 +3074,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1471300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1143700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>947700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>794600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>787700</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>737500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>672200</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3125,25 +3125,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>600</v>
+        <v>11500</v>
       </c>
       <c r="E61" s="3">
-        <v>500</v>
+        <v>16900</v>
       </c>
       <c r="F61" s="3">
-        <v>500</v>
+        <v>24100</v>
       </c>
       <c r="G61" s="3">
-        <v>500</v>
+        <v>17600</v>
       </c>
       <c r="H61" s="3">
-        <v>400</v>
+        <v>22600</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3176,25 +3176,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3394,11 +3394,11 @@
       <c r="H66" s="3">
         <v>813100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
+      <c r="I66" s="3">
+        <v>740700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>697900</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
@@ -3670,11 +3670,11 @@
       <c r="H72" s="3">
         <v>93800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
+      <c r="I72" s="3">
+        <v>81800</v>
+      </c>
+      <c r="J72" s="3">
+        <v>69300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
@@ -4032,11 +4032,11 @@
       <c r="H81" s="3">
         <v>13000</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
+      <c r="I81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>8100</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -4104,11 +4104,11 @@
       <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
+      <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>800</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -4410,11 +4410,11 @@
       <c r="H89" s="3">
         <v>14300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
+      <c r="I89" s="3">
+        <v>12600</v>
+      </c>
+      <c r="J89" s="3">
+        <v>8800</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -4482,11 +4482,11 @@
       <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
+      <c r="I91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1300</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
@@ -4635,11 +4635,11 @@
       <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
+      <c r="I94" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-79200</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -4693,25 +4693,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3700</v>
+        <v>3700</v>
       </c>
       <c r="E96" s="3">
-        <v>-6900</v>
+        <v>6900</v>
       </c>
       <c r="F96" s="3">
-        <v>-2300</v>
+        <v>2300</v>
       </c>
       <c r="G96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4911,11 +4911,11 @@
       <c r="H100" s="3">
         <v>69400</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
+      <c r="I100" s="3">
+        <v>40900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>70900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -4947,26 +4947,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5013,11 +5013,11 @@
       <c r="H102" s="3">
         <v>76300</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
+      <c r="I102" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>400</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>NECB</t>
   </si>
@@ -656,129 +656,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40543</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40178</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>39813</v>
       </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E8" s="3">
         <v>99800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>65100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>42000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>40700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>39600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>19900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21900</v>
       </c>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -827,36 +833,39 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E10" s="3">
         <v>99800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>42000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>40700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>40900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>39600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -878,9 +887,12 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -900,8 +912,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -950,9 +963,12 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,35 +1017,38 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1052,9 +1071,12 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1065,22 +1087,22 @@
         <v>1200</v>
       </c>
       <c r="F15" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="3">
         <v>1100</v>
       </c>
       <c r="H15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I15" s="3">
         <v>900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>800</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1103,9 +1125,12 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,110 +1147,117 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E17" s="3">
         <v>35000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E18" s="3">
         <v>64800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>16700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1245,110 +1277,117 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-14200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-14400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9600</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E21" s="3">
         <v>66000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4000</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1373,8 +1412,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1397,111 +1436,120 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E23" s="3">
         <v>64700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>15600</v>
       </c>
       <c r="G23" s="3">
         <v>15600</v>
       </c>
       <c r="H23" s="3">
+        <v>15600</v>
+      </c>
+      <c r="I23" s="3">
         <v>16900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3300</v>
       </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E24" s="3">
         <v>18500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1550,111 +1598,120 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E26" s="3">
         <v>46300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>13000</v>
       </c>
       <c r="I26" s="3">
         <v>13000</v>
       </c>
       <c r="J26" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K26" s="3">
         <v>8100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2200</v>
       </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E27" s="3">
         <v>46300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2200</v>
       </c>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1703,9 +1760,12 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1754,9 +1814,12 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1805,9 +1868,12 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1856,111 +1922,120 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>14200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>14400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9600</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E33" s="3">
         <v>46300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>13000</v>
       </c>
       <c r="I33" s="3">
         <v>13000</v>
       </c>
       <c r="J33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K33" s="3">
         <v>8100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2009,116 +2084,125 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E35" s="3">
         <v>46300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>13000</v>
       </c>
       <c r="I35" s="3">
         <v>13000</v>
       </c>
       <c r="J35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K35" s="3">
         <v>8100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40543</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40178</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>39813</v>
       </c>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2138,8 +2222,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2159,59 +2244,63 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E41" s="3">
         <v>68700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>95300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>152300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>127700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>51400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43200</v>
-      </c>
-      <c r="L41" s="3">
-        <v>3700</v>
       </c>
       <c r="M41" s="3">
         <v>3700</v>
       </c>
       <c r="N41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O41" s="3">
         <v>2800</v>
-      </c>
-      <c r="O41" s="3">
-        <v>2500</v>
       </c>
       <c r="P41" s="3">
         <v>2500</v>
       </c>
       <c r="Q41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R41" s="3">
         <v>3400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2400</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3"/>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2234,35 +2323,38 @@
         <v>100</v>
       </c>
       <c r="J42" s="3">
+        <v>100</v>
+      </c>
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3">
-        <v>32400</v>
+      <c r="L42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M42" s="3">
         <v>32400</v>
       </c>
       <c r="N42" s="3">
+        <v>32400</v>
+      </c>
+      <c r="O42" s="3">
         <v>48200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>84300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>46800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>96300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>37000</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2287,8 +2379,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2311,36 +2403,39 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3"/>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1500</v>
+        <v>5100</v>
       </c>
       <c r="E44" s="3">
         <v>1500</v>
       </c>
       <c r="F44" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G44" s="3">
         <v>2000</v>
       </c>
       <c r="H44" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="I44" s="3">
         <v>2200</v>
       </c>
       <c r="J44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K44" s="3">
         <v>2500</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2362,36 +2457,39 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
         <v>12300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2413,36 +2511,39 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E46" s="3">
         <v>82500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>105500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>158600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>133900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>57700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2464,44 +2565,47 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3"/>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E47" s="3">
         <v>34800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2515,60 +2619,66 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E48" s="3">
         <v>30400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
-        <v>11700</v>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>11700</v>
       </c>
       <c r="N48" s="3">
+        <v>11700</v>
+      </c>
+      <c r="O48" s="3">
         <v>12900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4400</v>
       </c>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3"/>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2576,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>700</v>
       </c>
       <c r="G49" s="3">
         <v>700</v>
@@ -2588,38 +2698,41 @@
         <v>700</v>
       </c>
       <c r="I49" s="3">
+        <v>700</v>
+      </c>
+      <c r="J49" s="3">
         <v>800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1000</v>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M49" s="3">
         <v>1000</v>
       </c>
       <c r="N49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O49" s="3">
         <v>1500</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1800</v>
       </c>
       <c r="P49" s="3">
         <v>1800</v>
       </c>
       <c r="Q49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R49" s="3">
         <v>1900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2000</v>
       </c>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3"/>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2668,9 +2781,12 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-      <c r="S50" s="3"/>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3"/>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2719,44 +2835,47 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3"/>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E52" s="3">
         <v>30700</v>
-      </c>
-      <c r="E52" s="3">
-        <v>29400</v>
       </c>
       <c r="F52" s="3">
         <v>29400</v>
       </c>
       <c r="G52" s="3">
+        <v>29400</v>
+      </c>
+      <c r="H52" s="3">
         <v>29000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30900</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>3700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
+      <c r="N52" s="3">
+        <v>3700</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
@@ -2770,9 +2889,12 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3"/>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2821,60 +2943,66 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2009600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1764100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1425000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1225100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>968200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>955200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>870300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>814800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>734500</v>
-      </c>
-      <c r="L54" s="3">
-        <v>515400</v>
       </c>
       <c r="M54" s="3">
         <v>515400</v>
       </c>
       <c r="N54" s="3">
+        <v>515400</v>
+      </c>
+      <c r="O54" s="3">
         <v>444200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>489300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>466000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>527300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>424200</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3"/>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2894,8 +3022,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2915,86 +3044,90 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1407700</v>
+        <v>1677500</v>
       </c>
       <c r="E57" s="3">
+        <v>1406600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1130900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>934800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>775200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>782800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>690400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>627600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4200</v>
+      <c r="L57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M57" s="3">
         <v>4200</v>
       </c>
       <c r="N57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5200</v>
       </c>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3"/>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>57700</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>7000</v>
+        <v>57000</v>
       </c>
       <c r="F58" s="3">
         <v>7000</v>
       </c>
       <c r="G58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H58" s="3">
         <v>14000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>42500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3016,9 +3149,12 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3"/>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3052,8 +3188,8 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -3067,36 +3203,39 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1471300</v>
+        <v>1685000</v>
       </c>
       <c r="E60" s="3">
+        <v>1469600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1143700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>947700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>794600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>787700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>737500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>672200</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3118,36 +3257,39 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3"/>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11500</v>
+        <v>3900</v>
       </c>
       <c r="E61" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F61" s="3">
         <v>16900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>22500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3169,35 +3311,38 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3"/>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="E62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F62" s="3">
         <v>2400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3200</v>
       </c>
       <c r="J62" s="3">
         <v>3200</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3220,9 +3365,12 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3"/>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3271,9 +3419,12 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3"/>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3322,9 +3473,12 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3373,60 +3527,66 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3"/>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1691200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1484800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1163000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>973700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>814400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>813100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>740700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>697900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
-        <v>411600</v>
+      <c r="L66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M66" s="3">
         <v>411600</v>
       </c>
       <c r="N66" s="3">
+        <v>411600</v>
+      </c>
+      <c r="O66" s="3">
         <v>340400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>382200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>357900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>419800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>313700</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3446,8 +3606,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3496,9 +3657,12 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3547,9 +3711,12 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3"/>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3598,9 +3765,12 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3"/>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3649,60 +3819,66 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-      <c r="S71" s="3"/>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3"/>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E72" s="3">
         <v>175500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>132700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>114300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>105300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>93800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>81800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>69300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
-        <v>55500</v>
+      <c r="L72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M72" s="3">
         <v>55500</v>
       </c>
       <c r="N72" s="3">
+        <v>55500</v>
+      </c>
+      <c r="O72" s="3">
         <v>53900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>57100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>55300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>54100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>57400</v>
       </c>
-      <c r="S72" s="3"/>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3"/>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3751,9 +3927,12 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-      <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3"/>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3802,9 +3981,12 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-      <c r="S74" s="3"/>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3"/>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3853,38 +4035,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3"/>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>318300</v>
+      </c>
+      <c r="E76" s="3">
         <v>279300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>262000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>251400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>153800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>142100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>129600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>116900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>109500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>103800</v>
       </c>
       <c r="M76" s="3">
         <v>103800</v>
@@ -3893,20 +4078,23 @@
         <v>103800</v>
       </c>
       <c r="O76" s="3">
+        <v>103800</v>
+      </c>
+      <c r="P76" s="3">
         <v>107100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>108100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>107400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>110500</v>
       </c>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3955,116 +4143,125 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3"/>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40543</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40178</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>39813</v>
       </c>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2"/>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E81" s="3">
         <v>46300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>13000</v>
       </c>
       <c r="I81" s="3">
         <v>13000</v>
       </c>
       <c r="J81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K81" s="3">
         <v>8100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3"/>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4084,8 +4281,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4096,22 +4294,22 @@
         <v>1200</v>
       </c>
       <c r="F83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
+      <c r="K83" s="3">
+        <v>800</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
@@ -4119,24 +4317,27 @@
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
-        <v>700</v>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
       </c>
       <c r="P83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q83" s="3">
         <v>800</v>
       </c>
       <c r="R83" s="3">
+        <v>800</v>
+      </c>
+      <c r="S83" s="3">
         <v>700</v>
       </c>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3"/>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4185,9 +4386,12 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3"/>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4236,9 +4440,12 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3"/>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4287,9 +4494,12 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3"/>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4338,9 +4548,12 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3"/>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4389,60 +4602,66 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3"/>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E89" s="3">
         <v>42800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>27500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1700</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>1700</v>
       </c>
       <c r="N89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O89" s="3">
         <v>600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3200</v>
       </c>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3"/>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4462,59 +4681,63 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3"/>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3"/>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4563,9 +4786,12 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3"/>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4614,60 +4840,66 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3"/>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-357800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-256600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-178900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-72100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-45800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-79200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>7000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>13100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-53700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-84200</v>
       </c>
-      <c r="S94" s="3"/>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3"/>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4687,49 +4919,50 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E96" s="3">
         <v>3700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>6900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>800</v>
-      </c>
-      <c r="I96" s="3">
-        <v>600</v>
       </c>
       <c r="J96" s="3">
         <v>600</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L96" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-500</v>
       </c>
       <c r="N96" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O96" s="3">
         <v>-700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-700</v>
       </c>
       <c r="Q96" s="3">
         <v>-700</v>
@@ -4737,9 +4970,12 @@
       <c r="R96" s="3">
         <v>-700</v>
       </c>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T96" s="3"/>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4788,9 +5024,12 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-      <c r="S97" s="3"/>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3"/>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4839,9 +5078,12 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-      <c r="S98" s="3"/>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3"/>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4890,60 +5132,66 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-      <c r="S99" s="3"/>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3"/>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E100" s="3">
         <v>288400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>172100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>240400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>69400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>40900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>70900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>-41000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>108800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>78400</v>
       </c>
-      <c r="S100" s="3"/>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3"/>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4968,17 +5216,17 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4992,58 +5240,64 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3"/>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3"/>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-57000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-58500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>76300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-17700</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M102" s="3">
         <v>-17700</v>
       </c>
       <c r="N102" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="O102" s="3">
         <v>-33300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>52200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2600</v>
       </c>
-      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NECB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>NECB</t>
   </si>
@@ -656,135 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40543</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40178</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>39813</v>
       </c>
-      <c r="T7" s="2"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E8" s="3">
         <v>104800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>99800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>65100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3">
         <v>19900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21900</v>
       </c>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -836,39 +842,42 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E10" s="3">
         <v>104800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>99800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>65100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>42000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>40700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -890,9 +899,12 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -913,8 +925,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,9 +979,12 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1020,9 +1036,12 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,26 +1051,26 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1074,9 +1093,12 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1090,22 +1112,22 @@
         <v>1200</v>
       </c>
       <c r="G15" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H15" s="3">
         <v>1100</v>
       </c>
       <c r="I15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J15" s="3">
         <v>900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>800</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1128,9 +1150,12 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,116 +1173,123 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E17" s="3">
         <v>38300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>3200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9000</v>
       </c>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3"/>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E18" s="3">
         <v>66500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>64800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>35500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>16700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13000</v>
       </c>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,116 +1310,123 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-14200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-14400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9600</v>
       </c>
-      <c r="T20" s="3"/>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3"/>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E21" s="3">
         <v>67000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>66000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>-4100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4000</v>
       </c>
-      <c r="T21" s="3"/>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3"/>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1415,8 +1454,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1439,117 +1478,126 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3"/>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3"/>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E23" s="3">
         <v>65800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>64700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>15600</v>
       </c>
       <c r="H23" s="3">
         <v>15600</v>
       </c>
       <c r="I23" s="3">
+        <v>15600</v>
+      </c>
+      <c r="J23" s="3">
         <v>16900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3300</v>
       </c>
-      <c r="T23" s="3"/>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3"/>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E24" s="3">
         <v>18700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1200</v>
       </c>
-      <c r="T24" s="3"/>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3"/>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1601,117 +1649,126 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-      <c r="T25" s="3"/>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3"/>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E26" s="3">
         <v>47100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>13000</v>
       </c>
       <c r="J26" s="3">
         <v>13000</v>
       </c>
       <c r="K26" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L26" s="3">
         <v>8100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2200</v>
       </c>
-      <c r="T26" s="3"/>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3"/>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E27" s="3">
         <v>47100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>46300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2200</v>
       </c>
-      <c r="T27" s="3"/>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3"/>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1763,9 +1820,12 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-      <c r="T28" s="3"/>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3"/>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1817,9 +1877,12 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3"/>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3"/>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1871,9 +1934,12 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-      <c r="T30" s="3"/>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3"/>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1925,117 +1991,126 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-      <c r="T31" s="3"/>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3"/>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>14200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>14400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9600</v>
       </c>
-      <c r="T32" s="3"/>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E33" s="3">
         <v>47100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>46300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>13000</v>
       </c>
       <c r="J33" s="3">
         <v>13000</v>
       </c>
       <c r="K33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L33" s="3">
         <v>8100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3"/>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2087,122 +2162,131 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-      <c r="T34" s="3"/>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E35" s="3">
         <v>47100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>46300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>13000</v>
       </c>
       <c r="J35" s="3">
         <v>13000</v>
       </c>
       <c r="K35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L35" s="3">
         <v>8100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3"/>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40543</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40178</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>39813</v>
       </c>
-      <c r="T38" s="2"/>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2223,8 +2307,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2245,62 +2330,66 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E41" s="3">
         <v>78300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>95300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>152300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>127700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>51400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43200</v>
-      </c>
-      <c r="M41" s="3">
-        <v>3700</v>
       </c>
       <c r="N41" s="3">
         <v>3700</v>
       </c>
       <c r="O41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P41" s="3">
         <v>2800</v>
-      </c>
-      <c r="P41" s="3">
-        <v>2500</v>
       </c>
       <c r="Q41" s="3">
         <v>2500</v>
       </c>
       <c r="R41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S41" s="3">
         <v>3400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2400</v>
       </c>
-      <c r="T41" s="3"/>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2326,35 +2415,38 @@
         <v>100</v>
       </c>
       <c r="K42" s="3">
+        <v>100</v>
+      </c>
+      <c r="L42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M42" s="3">
-        <v>32400</v>
+      <c r="M42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N42" s="3">
         <v>32400</v>
       </c>
       <c r="O42" s="3">
+        <v>32400</v>
+      </c>
+      <c r="P42" s="3">
         <v>48200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>84300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>46800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>96300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>37000</v>
       </c>
-      <c r="T42" s="3"/>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2382,8 +2474,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2406,39 +2498,42 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3"/>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3">
         <v>5100</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1500</v>
       </c>
       <c r="F44" s="3">
         <v>1500</v>
       </c>
       <c r="G44" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H44" s="3">
         <v>2000</v>
       </c>
       <c r="I44" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J44" s="3">
         <v>2200</v>
       </c>
       <c r="K44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L44" s="3">
         <v>2500</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2460,39 +2555,42 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-      <c r="T44" s="3"/>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E45" s="3">
         <v>13500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2514,39 +2612,42 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3"/>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E46" s="3">
         <v>97000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>82500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>105500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>158600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>133900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>57700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2568,47 +2669,50 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-      <c r="T46" s="3"/>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E47" s="3">
         <v>36900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>39300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2622,63 +2726,69 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3"/>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E48" s="3">
         <v>29200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
-        <v>11700</v>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N48" s="3">
         <v>11700</v>
       </c>
       <c r="O48" s="3">
+        <v>11700</v>
+      </c>
+      <c r="P48" s="3">
         <v>12900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4400</v>
       </c>
-      <c r="T48" s="3"/>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3"/>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2689,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>700</v>
       </c>
       <c r="H49" s="3">
         <v>700</v>
@@ -2701,38 +2811,41 @@
         <v>700</v>
       </c>
       <c r="J49" s="3">
+        <v>700</v>
+      </c>
+      <c r="K49" s="3">
         <v>800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1000</v>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N49" s="3">
         <v>1000</v>
       </c>
       <c r="O49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P49" s="3">
         <v>1500</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1800</v>
       </c>
       <c r="Q49" s="3">
         <v>1800</v>
       </c>
       <c r="R49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S49" s="3">
         <v>1900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2000</v>
       </c>
-      <c r="T49" s="3"/>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3"/>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2784,9 +2897,12 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-      <c r="T50" s="3"/>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3"/>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2838,47 +2954,50 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-      <c r="T51" s="3"/>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3"/>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E52" s="3">
         <v>34400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>29400</v>
       </c>
       <c r="G52" s="3">
         <v>29400</v>
       </c>
       <c r="H52" s="3">
+        <v>29400</v>
+      </c>
+      <c r="I52" s="3">
         <v>29000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30900</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>3700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
+      <c r="O52" s="3">
+        <v>3700</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
@@ -2892,9 +3011,12 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3"/>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3"/>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2946,63 +3068,69 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-      <c r="T53" s="3"/>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3"/>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2063500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2009600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1764100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1425000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1225100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>968200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>955200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>870300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>814800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>734500</v>
-      </c>
-      <c r="M54" s="3">
-        <v>515400</v>
       </c>
       <c r="N54" s="3">
         <v>515400</v>
       </c>
       <c r="O54" s="3">
+        <v>515400</v>
+      </c>
+      <c r="P54" s="3">
         <v>444200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>489300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>466000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>527300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>424200</v>
       </c>
-      <c r="T54" s="3"/>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3"/>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3023,8 +3151,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3045,92 +3174,96 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1626100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1677500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1406600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1130900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>934800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>775200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>782800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>690400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>627600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
-        <v>4200</v>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N57" s="3">
         <v>4200</v>
       </c>
       <c r="O57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5200</v>
       </c>
-      <c r="T57" s="3"/>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3"/>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>800</v>
+        <v>70900</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>57000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7000</v>
       </c>
       <c r="G58" s="3">
         <v>7000</v>
       </c>
       <c r="H58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I58" s="3">
         <v>14000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>42500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>40400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3152,9 +3285,12 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3"/>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3"/>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3191,8 +3327,8 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3206,39 +3342,42 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-      <c r="T59" s="3"/>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3"/>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1685000</v>
+        <v>1704300</v>
       </c>
       <c r="E60" s="3">
+        <v>1684200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1469600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1143700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>947700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>794600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>787700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>737500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>672200</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3260,39 +3399,42 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-      <c r="T60" s="3"/>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3"/>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F61" s="3">
         <v>12200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22600</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>22500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3314,38 +3456,41 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-      <c r="T61" s="3"/>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3"/>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3200</v>
       </c>
       <c r="K62" s="3">
         <v>3200</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3368,9 +3513,12 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3"/>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3422,9 +3570,12 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-      <c r="T63" s="3"/>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3"/>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3476,9 +3627,12 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-      <c r="T64" s="3"/>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3"/>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3530,63 +3684,69 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-      <c r="T65" s="3"/>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1711800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1691200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1484800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1163000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>973700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>814400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>813100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>740700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>697900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3">
-        <v>411600</v>
+      <c r="M66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N66" s="3">
         <v>411600</v>
       </c>
       <c r="O66" s="3">
+        <v>411600</v>
+      </c>
+      <c r="P66" s="3">
         <v>340400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>382200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>357900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>419800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>313700</v>
       </c>
-      <c r="T66" s="3"/>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3607,8 +3767,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3660,9 +3821,12 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-      <c r="T68" s="3"/>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3"/>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3714,9 +3878,12 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-      <c r="T69" s="3"/>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3768,9 +3935,12 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-      <c r="T70" s="3"/>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3822,63 +3992,69 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-      <c r="T71" s="3"/>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3"/>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E72" s="3">
         <v>214000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>175500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>132700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>114300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>105300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>93800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>81800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>69300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
-        <v>55500</v>
+      <c r="M72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N72" s="3">
         <v>55500</v>
       </c>
       <c r="O72" s="3">
+        <v>55500</v>
+      </c>
+      <c r="P72" s="3">
         <v>53900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>55300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>54100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>57400</v>
       </c>
-      <c r="T72" s="3"/>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3"/>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3930,9 +4106,12 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-      <c r="T73" s="3"/>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3984,9 +4163,12 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-      <c r="T74" s="3"/>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4038,41 +4220,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-      <c r="T75" s="3"/>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3"/>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>351700</v>
+      </c>
+      <c r="E76" s="3">
         <v>318300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>279300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>262000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>251400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>153800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>142100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>129600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>116900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>109500</v>
-      </c>
-      <c r="M76" s="3">
-        <v>103800</v>
       </c>
       <c r="N76" s="3">
         <v>103800</v>
@@ -4081,20 +4266,23 @@
         <v>103800</v>
       </c>
       <c r="P76" s="3">
+        <v>103800</v>
+      </c>
+      <c r="Q76" s="3">
         <v>107100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>108100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>107400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>110500</v>
       </c>
-      <c r="T76" s="3"/>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3"/>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4146,122 +4334,131 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-      <c r="T77" s="3"/>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3"/>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40543</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40178</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>39813</v>
       </c>
-      <c r="T80" s="2"/>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2"/>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E81" s="3">
         <v>47100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>46300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>13000</v>
       </c>
       <c r="J81" s="3">
         <v>13000</v>
       </c>
       <c r="K81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L81" s="3">
         <v>8100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3"/>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3"/>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4282,8 +4479,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4297,22 +4495,22 @@
         <v>1200</v>
       </c>
       <c r="G83" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H83" s="3">
         <v>1100</v>
       </c>
       <c r="I83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J83" s="3">
         <v>900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
+      <c r="L83" s="3">
+        <v>800</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
@@ -4320,24 +4518,27 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>700</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
       </c>
       <c r="Q83" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>800</v>
       </c>
       <c r="S83" s="3">
+        <v>800</v>
+      </c>
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3"/>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3"/>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4389,9 +4590,12 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-      <c r="T84" s="3"/>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3"/>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4443,9 +4647,12 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-      <c r="T85" s="3"/>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3"/>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4497,9 +4704,12 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-      <c r="T86" s="3"/>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3"/>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4551,9 +4761,12 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-      <c r="T87" s="3"/>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3"/>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4605,63 +4818,69 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-      <c r="T88" s="3"/>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3"/>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E89" s="3">
         <v>48700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>42800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>1700</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N89" s="3">
         <v>1700</v>
       </c>
       <c r="O89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P89" s="3">
         <v>600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3200</v>
       </c>
-      <c r="T89" s="3"/>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3"/>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4682,62 +4901,66 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3"/>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3"/>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4789,9 +5012,12 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-      <c r="T92" s="3"/>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3"/>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4843,63 +5069,69 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-      <c r="T93" s="3"/>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3"/>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-234000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-357800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-256600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-178900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-72100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-45800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-79200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>7000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>13100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-53700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-84200</v>
       </c>
-      <c r="T94" s="3"/>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3"/>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4920,52 +5152,53 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E96" s="3">
         <v>7900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>6900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>600</v>
       </c>
       <c r="K96" s="3">
         <v>600</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M96" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>-500</v>
       </c>
       <c r="O96" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P96" s="3">
         <v>-700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-700</v>
       </c>
       <c r="R96" s="3">
         <v>-700</v>
@@ -4973,9 +5206,12 @@
       <c r="S96" s="3">
         <v>-700</v>
       </c>
-      <c r="T96" s="3"/>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U96" s="3"/>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5027,9 +5263,12 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-      <c r="T97" s="3"/>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3"/>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5081,9 +5320,12 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-      <c r="T98" s="3"/>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3"/>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5135,63 +5377,69 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-      <c r="T99" s="3"/>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3"/>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>194900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>288400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>172100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>240400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>69400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>70900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-41000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>18100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-64000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>108800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>78400</v>
       </c>
-      <c r="T100" s="3"/>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3"/>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5219,17 +5467,17 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5243,61 +5491,67 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3"/>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3"/>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>9600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-57000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>83100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-58500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>76300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-17700</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N102" s="3">
         <v>-17700</v>
       </c>
       <c r="O102" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="P102" s="3">
         <v>-33300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-44300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>52200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2600</v>
       </c>
-      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
